--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104744_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104744_W32.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8723</v>
+        <v>10.6845</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1286</v>
+        <v>7.9851</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7437</v>
+        <v>2.6995</v>
       </c>
       <c r="G2" t="n">
-        <v>8.2661</v>
+        <v>8.259</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4855</v>
+        <v>3.4837</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7807</v>
+        <v>4.7753</v>
       </c>
       <c r="J2" t="n">
-        <v>7.126</v>
+        <v>7.1095</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3353</v>
+        <v>3.3267</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7907</v>
+        <v>3.7828</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1402</v>
+        <v>1.1495</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1502</v>
+        <v>0.157</v>
       </c>
       <c r="O2" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7801</v>
+        <v>-0.9615</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.044</v>
+        <v>-0.1652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7361</v>
+        <v>-0.7962</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0231</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8866</v>
+        <v>4.2577</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7203</v>
+        <v>3.1975</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1663</v>
+        <v>1.0602</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9756</v>
+        <v>1.9451</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1781</v>
+        <v>1.2234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7976</v>
+        <v>0.7217</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3099</v>
+        <v>2.3312</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9678</v>
+        <v>2.0717</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3421</v>
+        <v>0.2596</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3342</v>
+        <v>-0.3861</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2103</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5446</v>
+        <v>0.4622</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8175</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8175</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0935</v>
+        <v>-1.0045</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4104</v>
+        <v>-0.1745</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3169</v>
+        <v>-0.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6429</v>
+        <v>4.1504</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6311</v>
+        <v>2.784</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0117</v>
+        <v>1.3665</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9508</v>
+        <v>1.9787</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2232</v>
+        <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7276</v>
+        <v>0.7986</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3481</v>
+        <v>2.3058</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0798</v>
+        <v>0.9653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2683</v>
+        <v>1.3405</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3972</v>
+        <v>-0.3271</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8566</v>
+        <v>0.2148</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4594</v>
+        <v>-0.5419</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2719</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6264</v>
+        <v>0.3507</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7635</v>
+        <v>0.4782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8629</v>
+        <v>-0.1275</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1825</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5477</v>
+        <v>3.9187</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1512</v>
+        <v>2.7815</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3964</v>
+        <v>1.1371</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1273</v>
+        <v>3.4066</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4523</v>
+        <v>3.1832</v>
       </c>
       <c r="I5" t="n">
-        <v>1.675</v>
+        <v>0.2234</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5843</v>
+        <v>4.5218</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9565</v>
+        <v>3.6435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6278</v>
+        <v>0.8783</v>
       </c>
       <c r="M5" t="n">
-        <v>1.543</v>
+        <v>-1.1152</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4958</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0472</v>
+        <v>-0.6549</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8175</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8175</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2397</v>
+        <v>0.5819</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.3782</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7134</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6369</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3862</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0625</v>
+        <v>3.465</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9114</v>
+        <v>2.3669</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1511</v>
+        <v>1.098</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4162</v>
+        <v>3.7225</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1925</v>
+        <v>1.8607</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2237</v>
+        <v>1.8618</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5412</v>
+        <v>3.5784</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6584</v>
+        <v>2.5511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8828</v>
+        <v>1.0273</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.125</v>
+        <v>0.1442</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4659</v>
+        <v>-0.6904</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6591</v>
+        <v>0.8345</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2719</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0447</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2859</v>
+        <v>-1.1194</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5173</v>
+        <v>-0.3417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2314</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1594</v>
+        <v>1.6342</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0508</v>
+        <v>2.4655</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0333</v>
+        <v>1.3125</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0175</v>
+        <v>1.153</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7229</v>
+        <v>3.1274</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8588</v>
+        <v>1.453</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8641</v>
+        <v>1.6743</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5895</v>
+        <v>1.5766</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5576</v>
+        <v>0.9513</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0319</v>
+        <v>0.6254</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1334</v>
+        <v>1.5507</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6988</v>
+        <v>0.5018</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8322000000000001</v>
+        <v>1.049</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2272</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4991</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2719</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5362</v>
+        <v>-0.8487</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6941000000000001</v>
+        <v>0.1228</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8421</v>
+        <v>-0.9716</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0913</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6369</v>
+        <v>-0.387</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5456</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4291</v>
+        <v>2.3464</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9541</v>
+        <v>3.6471</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.525</v>
+        <v>-1.3007</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2734</v>
+        <v>1.7181</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6153999999999999</v>
+        <v>-2.5539</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8888</v>
+        <v>4.2719</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4254</v>
+        <v>2.7808</v>
       </c>
       <c r="K8" t="n">
-        <v>1.239</v>
+        <v>-0.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1864</v>
+        <v>3.3809</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6988</v>
+        <v>-1.0628</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6237</v>
+        <v>-1.9538</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0752</v>
+        <v>0.8911</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4991</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8175</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9978</v>
+        <v>-0.1928</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7771</v>
+        <v>0.0044</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2207</v>
+        <v>-0.1972</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3862</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2507</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9303</v>
+        <v>1.6325</v>
       </c>
       <c r="E9" t="n">
-        <v>3.185</v>
+        <v>2.3585</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2547</v>
+        <v>-0.726</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7162</v>
+        <v>-0.6902</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5599</v>
+        <v>0.2124</v>
       </c>
       <c r="I9" t="n">
-        <v>4.276</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7878</v>
+        <v>0.9581</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5988</v>
+        <v>1.003</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3866</v>
+        <v>-0.0449</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0716</v>
+        <v>-1.6483</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9611</v>
+        <v>-0.7906</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8894</v>
+        <v>-0.8578</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6034</v>
+        <v>0.4122</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4669</v>
+        <v>0.5386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1365</v>
+        <v>-0.1264</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6369</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7559</v>
+        <v>0.8423</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5894</v>
+        <v>1.3486</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8335</v>
+        <v>-0.5064</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6915</v>
+        <v>-0.2739</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2119</v>
+        <v>0.6121</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9034</v>
+        <v>-0.886</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9651</v>
+        <v>1.4165</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0083</v>
+        <v>1.2303</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0433</v>
+        <v>0.1862</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6566</v>
+        <v>-1.6904</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7965</v>
+        <v>-0.6182</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8601</v>
+        <v>-1.0722</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3631</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2272</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5903</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4613</v>
+        <v>1.4121</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2397</v>
+        <v>1.1888</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2216</v>
+        <v>0.2232</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5456</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0913</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5456</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6956</v>
+        <v>0.4597</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6703</v>
+        <v>2.4242</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9747</v>
+        <v>-1.9645</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7881</v>
+        <v>0.7875</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5012</v>
+        <v>0.4999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2869</v>
+        <v>0.2876</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2268</v>
+        <v>2.2201</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3048</v>
+        <v>1.3033</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4387</v>
+        <v>-1.4326</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0179</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.385</v>
+        <v>0.1487</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5113</v>
+        <v>0.2739</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1263</v>
+        <v>-0.1253</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1766</v>
+        <v>0.2221</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5108</v>
+        <v>-0.5757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6874</v>
+        <v>0.7977</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5457</v>
+        <v>1.5403</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3163</v>
+        <v>-1.3179</v>
       </c>
       <c r="I12" t="n">
-        <v>2.862</v>
+        <v>2.8583</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3726</v>
+        <v>0.3607</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1879</v>
+        <v>-2.1933</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5604</v>
+        <v>2.554</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1731</v>
+        <v>1.1796</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8754</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0953</v>
+        <v>-0.0498</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2526</v>
+        <v>0.2018</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3479</v>
+        <v>-0.2516</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.0503</v>
+        <v>34.44479999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>29.4639</v>
+        <v>29.6302</v>
       </c>
       <c r="F13" t="n">
-        <v>4.586200000000001</v>
+        <v>4.8144</v>
       </c>
       <c r="G13" t="n">
-        <v>25.544</v>
+        <v>25.5211</v>
       </c>
       <c r="H13" t="n">
-        <v>9.842700000000001</v>
+        <v>9.836600000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>15.7014</v>
+        <v>15.6842</v>
       </c>
       <c r="J13" t="n">
-        <v>29.2767</v>
+        <v>29.1595</v>
       </c>
       <c r="K13" t="n">
-        <v>13.9379</v>
+        <v>13.8664</v>
       </c>
       <c r="L13" t="n">
-        <v>15.3385</v>
+        <v>15.2934</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.732400000000001</v>
+        <v>-3.638500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.0956</v>
+        <v>-4.0295</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3629000000000001</v>
+        <v>0.3910999999999996</v>
       </c>
       <c r="P13" t="n">
-        <v>9.087300000000001</v>
+        <v>9.105499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3594</v>
+        <v>-11.3815</v>
       </c>
       <c r="R13" t="n">
-        <v>20.447</v>
+        <v>20.4869</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.672600000000001</v>
+        <v>-1.2711</v>
       </c>
       <c r="T13" t="n">
-        <v>2.179</v>
+        <v>2.5053</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.8516</v>
+        <v>-3.7767</v>
       </c>
       <c r="V13" t="n">
-        <v>1.091299999999999</v>
+        <v>1.089599999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>9.367799999999999</v>
+        <v>9.3468</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.276399999999999</v>
+        <v>-8.257300000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0059</v>
+        <v>1.219</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7415</v>
+        <v>4.3556</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2643</v>
+        <v>-3.1366</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2872</v>
+        <v>-0.0263</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2532</v>
+        <v>1.2411</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0339</v>
+        <v>-1.2674</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.08890000000000001</v>
+        <v>4.6612</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1262</v>
+        <v>3.6262</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>1.035</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1983</v>
+        <v>-4.6875</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1271</v>
+        <v>-2.3852</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0712</v>
+        <v>-2.3023</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9087</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-5.9184</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9087</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3843</v>
+        <v>0.8953</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8304</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.1851</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.9026</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.9026</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4838</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3962</v>
+        <v>0.7881</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9124</v>
+        <v>0.1539</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-1.2831</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2443</v>
+        <v>-1.2522</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2702</v>
+        <v>-0.0309</v>
       </c>
       <c r="J15" t="n">
-        <v>4.679</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6411</v>
+        <v>-0.1314</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0379</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.705</v>
+        <v>-1.189</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.3969</v>
+        <v>-1.1209</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3081</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.5437</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.9069</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3631</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1429</v>
+        <v>1.3146</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7134</v>
+        <v>0.8823</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4294</v>
+        <v>0.4324</v>
       </c>
       <c r="V15" t="n">
-        <v>4.9106</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4.9106</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2698</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7724</v>
+        <v>1.7648</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0422</v>
+        <v>-1.8425</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8385</v>
+        <v>0.8387</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0542</v>
+        <v>-1.0514</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8927</v>
+        <v>1.8901</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1194</v>
+        <v>2.1133</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6334</v>
+        <v>-0.6345</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7528</v>
+        <v>2.7479</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2809</v>
+        <v>-1.2747</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8601</v>
+        <v>-0.8578</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.347</v>
+        <v>-0.3485</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5788</v>
+        <v>-0.3888</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0807</v>
+        <v>-0.8437</v>
       </c>
       <c r="E17" t="n">
-        <v>0.129</v>
+        <v>0.3628</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2097</v>
+        <v>-1.2066</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8507</v>
+        <v>-0.8517</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3111</v>
+        <v>0.3103</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1617</v>
+        <v>-1.162</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0406</v>
+        <v>0.0377</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8295</v>
+        <v>0.8274</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8913</v>
+        <v>-0.8895</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5184</v>
+        <v>-0.5171</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3728</v>
+        <v>-0.3724</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.3251</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.3251</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3196</v>
+        <v>-1.1349</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2831</v>
+        <v>0.06</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0365</v>
+        <v>-1.1949</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8478</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.6388</v>
+        <v>0.7351</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.209</v>
+        <v>-1.4343</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1733</v>
+        <v>1.2493</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2112</v>
+        <v>1.1376</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0379</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6745</v>
+        <v>-1.9485</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4276</v>
+        <v>-0.4025</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2469</v>
+        <v>-1.546</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5282</v>
+        <v>-0.4389</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2533</v>
+        <v>-0.0512</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2749</v>
+        <v>-0.3878</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4584</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3943</v>
+        <v>-1.2933</v>
       </c>
       <c r="E19" t="n">
-        <v>0.066</v>
+        <v>0.168</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4604</v>
+        <v>-1.4612</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7018</v>
+        <v>-0.9006</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7348</v>
+        <v>0.4309</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4367</v>
+        <v>-1.3315</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2524</v>
+        <v>1.1204</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1406</v>
+        <v>1.1204</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1118</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9543</v>
+        <v>-2.021</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4058</v>
+        <v>-0.6895</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5485</v>
+        <v>-1.3315</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4544</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6816</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6917</v>
+        <v>0.2903</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0504</v>
+        <v>0.1857</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6413</v>
+        <v>0.1046</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4536</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5918</v>
+        <v>-2.5887</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0631</v>
+        <v>-1.4767</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5287</v>
+        <v>-1.112</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9014</v>
+        <v>-3.8428</v>
       </c>
       <c r="H20" t="n">
-        <v>0.432</v>
+        <v>-3.6361</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3335</v>
+        <v>-0.2068</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1233</v>
+        <v>-1.1788</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1233</v>
+        <v>-2.2138</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0247</v>
+        <v>-2.664</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6913</v>
+        <v>-1.4223</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3335</v>
+        <v>-1.2417</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6816</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4544</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.008800000000000001</v>
+        <v>1.2542</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0504</v>
+        <v>1.068</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0416</v>
+        <v>0.1862</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7882</v>
+        <v>-3.945</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4352</v>
+        <v>-0.5849</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3531</v>
+        <v>-3.36</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.303</v>
+        <v>-3.3062</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4004</v>
+        <v>-0.4044</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9026</v>
+        <v>-2.9018</v>
       </c>
       <c r="J21" t="n">
-        <v>0.55</v>
+        <v>0.5326</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2451</v>
+        <v>1.2336</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.695</v>
+        <v>-0.7009</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.8531</v>
+        <v>-3.8389</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6455</v>
+        <v>-1.638</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2076</v>
+        <v>-2.2009</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4683</v>
+        <v>0.3205</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4673</v>
+        <v>0.3456</v>
       </c>
       <c r="U21" t="n">
-        <v>0.001</v>
+        <v>-0.0251</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3543</v>
+        <v>-4.932</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5872</v>
+        <v>-4.3669</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7671</v>
+        <v>-0.5651</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1081</v>
+        <v>-3.1037</v>
       </c>
       <c r="H22" t="n">
-        <v>0.411</v>
+        <v>0.4132</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5191</v>
+        <v>-3.5169</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.137</v>
+        <v>-1.1423</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1924</v>
+        <v>1.1893</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3294</v>
+        <v>-2.3317</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9711</v>
+        <v>-1.9613</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1897</v>
+        <v>-1.1852</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0935</v>
+        <v>0.5179</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0254</v>
+        <v>0.2598</v>
       </c>
       <c r="U22" t="n">
-        <v>0.068</v>
+        <v>0.2581</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7542</v>
+        <v>-5.925</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3733</v>
+        <v>-2.1575</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3809</v>
+        <v>-3.7674</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4288</v>
+        <v>-4.4287</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4463</v>
+        <v>-1.4498</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9825</v>
+        <v>-2.9789</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6931</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6498</v>
+        <v>-0.6592</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0433</v>
+        <v>-0.0449</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.7357</v>
+        <v>-3.7246</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.9392</v>
+        <v>-2.934</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8033</v>
+        <v>0.0289</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1138</v>
+        <v>0.348</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9171</v>
+        <v>-0.3191</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6845</v>
+        <v>-6.9118</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0921</v>
+        <v>-1.7461</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5924</v>
+        <v>-5.1657</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6198</v>
+        <v>-3.613</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9761</v>
+        <v>-1.9683</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6437</v>
+        <v>-1.6448</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7152</v>
+        <v>-1.7201</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6161</v>
+        <v>-0.6173</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.0991</v>
+        <v>-1.1029</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9046</v>
+        <v>-1.8929</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.36</v>
+        <v>-1.351</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5446</v>
+        <v>-0.5419</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4048</v>
+        <v>-0.6434</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5363</v>
+        <v>-0.1838</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8685</v>
+        <v>-0.4596</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.1143</v>
+        <v>-3.1107</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.2738</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.302199999999999</v>
+        <v>-6.9737</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8574</v>
+        <v>-1.9293</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4448</v>
+        <v>-5.0443</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3079</v>
+        <v>-4.3043</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.2067</v>
+        <v>-3.2051</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1011</v>
+        <v>-1.0991</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2247</v>
+        <v>-1.2365</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8399</v>
+        <v>-0.8488</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3848</v>
+        <v>-0.3877</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.0831</v>
+        <v>-3.0678</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.3668</v>
+        <v>-2.3563</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7163</v>
+        <v>-0.7114</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1984</v>
+        <v>0.1242</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6561</v>
+        <v>0.2876</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5423</v>
+        <v>-0.1634</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.5687</v>
+        <v>-2.5659</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-34.0499</v>
+        <v>-32.4648</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.586299999999999</v>
+        <v>-4.7621</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.4639</v>
+        <v>-27.7024</v>
       </c>
       <c r="G26" t="n">
-        <v>-25.544</v>
+        <v>-25.5208</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.842499999999999</v>
+        <v>-9.8367</v>
       </c>
       <c r="I26" t="n">
-        <v>-15.7013</v>
+        <v>-15.6843</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7325</v>
+        <v>3.638499999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>4.095400000000001</v>
+        <v>4.0295</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3627999999999997</v>
+        <v>-0.3908999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-29.2766</v>
+        <v>-29.1597</v>
       </c>
       <c r="N26" t="n">
-        <v>-13.9381</v>
+        <v>-13.8664</v>
       </c>
       <c r="O26" t="n">
-        <v>-15.3385</v>
+        <v>-15.2932</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.0876</v>
+        <v>-9.105300000000002</v>
       </c>
       <c r="Q26" t="n">
-        <v>-20.4468</v>
+        <v>-20.4869</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3592</v>
+        <v>11.3816</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6727</v>
+        <v>3.251300000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>3.8518</v>
+        <v>3.8288</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1792</v>
+        <v>-0.5774000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0912</v>
+        <v>-1.089500000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>8.276299999999999</v>
+        <v>8.257400000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.367799999999999</v>
+        <v>-9.346900000000002</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104744_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104744_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.257300000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104744_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.346900000000002</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
